--- a/experiment_results/wedos_grid/rtt_bursts_S4_atk1pct_wu500000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S4_atk1pct_wu500000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>96817</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>72961</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>54470</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22567</t>
+          <t>16820</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>28452</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
